--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -518,21 +518,21 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="21" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="21" customWidth="1" min="47" max="47"/>
+    <col width="24" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -851,10 +851,8 @@
           <t>machama maharjan</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9767968876</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9767968876</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -889,10 +887,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.736575236789317</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.73657523678932</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -930,10 +926,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH2" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH2" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI2" s="3" t="inlineStr">
         <is>
@@ -952,25 +946,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L29-2</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>27.736575236789317</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>27.73657523678932</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1007,7 +997,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:41 AM</t>
+          <t>18 Oct 2026 10:37 AM</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1033,22 +1023,22 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
+          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>stb box faulty</t>
+          <t>router damage issue</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>TKT1373949</t>
+          <t>TKT1373790</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>machama maharjan</t>
+          <t>Babu Raja Maharjan</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -1056,20 +1046,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>machama maharjan</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9767968876</t>
-        </is>
+          <t>Babu Raja Maharjan</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>9802243292</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1079,24 +1063,24 @@
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2026 09:29:55 PM</t>
+          <t>17 Oct 2026 04:53:20 PM</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>KLK9767968876</t>
+          <t>9802243292</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2026 09:25:44 PM</t>
+          <t>17 Oct 2026 04:49:27 PM</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:41:52 AM</t>
+          <t>18 Oct 2026 10:37:10 AM</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
@@ -1104,10 +1088,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.736575236789317</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.74316</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1116,7 +1098,7 @@
       </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>Layer 2-CG Group</t>
+          <t>Layer 1-</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
@@ -1126,40 +1108,36 @@
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AD3" s="3" t="inlineStr"/>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>27.736575236789317, 27.736575236789317, Kathmandu, Nepal, Nepal</t>
+          <t>basundhara chauki near Southwestern State College, Bagmati, Central, Nepal</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
-          <t>9767968876@gmail.com</t>
+          <t>baburajmaharjan@gmail.com</t>
         </is>
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
-        </is>
-      </c>
-      <c r="AH3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
       <c r="AI3" s="3" t="inlineStr">
         <is>
-          <t>00:00 hour</t>
+          <t>03:11 hour</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
       <c r="AK3" s="3" t="inlineStr"/>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t>Dinesh Rawat</t>
+          <t>Aakash Shah</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
@@ -1167,35 +1145,31 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
-          <t>L29-2</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>27.736575236789317</t>
-        </is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="n">
+        <v>85.33889000000001</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>13h 11m</t>
+          <t>17h 43m</t>
         </is>
       </c>
       <c r="AT3" s="3" t="inlineStr">
         <is>
-          <t>13h 16m</t>
+          <t>17h 47m</t>
         </is>
       </c>
       <c r="AU3" s="3" t="inlineStr">
@@ -1205,7 +1179,7 @@
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
+          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="AW3" s="3" t="inlineStr">
@@ -1222,7 +1196,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:37 AM</t>
+          <t>18 Oct 2026 10:36 AM</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1271,20 +1245,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Babu Raja Maharjan</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9802243292</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9802243292</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1319,10 +1287,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.74316</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.74316</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1378,25 +1344,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.33889</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.33889000000001</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1428,22 +1390,22 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:36 AM</t>
+          <t>18 Oct 2026 10:59 AM</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1459,70 +1421,70 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>router damage issue</t>
+          <t>iptv issue</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>TKT1373790</t>
+          <t>TKT1373564</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Babu Raja Maharjan</t>
+          <t>Dharma Ratna shakya</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>Babu Raja Maharjan</t>
+          <t>Dharma Ratna shakya</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>9802243292</t>
+          <t>9841593447</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2026 04:53:20 PM</t>
+          <t>18 Oct 2026 10:59:14 AM</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>9802243292</t>
+          <t>9841593447</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2026 04:49:27 PM</t>
+          <t>17 Oct 2026 11:56:46 AM</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:37:10 AM</t>
+          <t>18 Oct 2026 10:59:14 AM</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
@@ -1530,109 +1492,97 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.74316</t>
-        </is>
-      </c>
+      <c r="Y5" s="3" t="inlineStr"/>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>Layer 1-</t>
+          <t>Layer 1-User</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>Laxman Koirala</t>
+          <t>L1  Support</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>basundhara chauki near Southwestern State College, Bagmati, Central, Nepal</t>
-        </is>
-      </c>
-      <c r="AF5" s="3" t="inlineStr">
-        <is>
-          <t>baburajmaharjan@gmail.com</t>
-        </is>
-      </c>
+          <t>27.669819, 85.326742, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr"/>
       <c r="AG5" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="AH5" s="3" t="inlineStr"/>
       <c r="AI5" s="3" t="inlineStr">
         <is>
-          <t>03:11 hour</t>
+          <t>08:04 hour</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t>Aakash Shah</t>
+          <t>Nirmaya Mukhiya</t>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="AN5" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
-          <t>2,7</t>
-        </is>
-      </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.33889</t>
-        </is>
-      </c>
+          <t>L107-5</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>17h 43m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>17h 47m</t>
+          <t>23h 2m</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="AW5" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -1647,15 +1597,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
@@ -1717,7 +1667,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>15h 27m</t>
+          <t>12h 9m</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1679,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>15h 31m</t>
+          <t>17h 58m</t>
         </is>
       </c>
     </row>
@@ -1770,10 +1720,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -1781,61 +1731,56 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>IPTV STB box Damage Issue</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1847,239 +1792,151 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TKT1373949</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>machama maharjan</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>IPTV STB box Damage Issue</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 09:29:55 PM</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 09:25:44 PM</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>18 Oct 2026 10:41:52 AM</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>13h 11m</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>13h 16m</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>TKT1373949</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>machama maharjan</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>IPTV STB box Damage Issue</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 09:29:55 PM</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 09:25:44 PM</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>18 Oct 2026 10:41:52 AM</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>13h 11m</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>13h 16m</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TKT1373790</t>
+          <t>TKT1373949</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Babu Raja Maharjan</t>
+          <t>machama maharjan</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -2089,7 +1946,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2104,37 +1961,37 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>17 Oct 2026 04:53:20 PM</t>
+          <t>17 Oct 2026 09:29:55 PM</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>17 Oct 2026 04:49:27 PM</t>
+          <t>17 Oct 2026 09:25:44 PM</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:37:10 AM</t>
+          <t>18 Oct 2026 10:41:52 AM</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>17h 43m</t>
+          <t>13h 11m</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>17h 47m</t>
+          <t>13h 16m</t>
         </is>
       </c>
     </row>
@@ -2171,37 +2028,171 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
           <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 04:53:20 PM</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 04:49:27 PM</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 10:37:10 AM</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>17h 43m</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>17h 47m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1373790</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Babu Raja Maharjan</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>17 Oct 2026 04:53:20 PM</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>17 Oct 2026 04:49:27 PM</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>18 Oct 2026 10:37:10 AM</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>17h 43m</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>17h 47m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373564</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Dharma Ratna shakya</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 10:59:14 AM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:56:46 AM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 10:59:14 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>23h 2m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1454,10 +1454,8 @@
           <t>Dharma Ratna shakya</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9841593447</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9841593447</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1543,10 +1541,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
@@ -1557,7 +1553,7 @@
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1606,7 +1602,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2162,7 +2158,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -529,10 +529,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -1579,6 +1579,412 @@
       <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:35 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373226</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Mainali</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Mainali</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9851330557</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:13:58 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9851330557</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:13:58 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:35:33 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>27.75457483862807, 85.32602632379277, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L36-1</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 21m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 21m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:32 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372734</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Ram Dhayal Mahato</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Ram Dhayal Mahato</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9841455936</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:11:07 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9841455936</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:11:07 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:32:58 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.73283</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Chundevi Temple Kathmandu 27.73548, 85.33781, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>ramdayal202011@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>17:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L43-5</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.33553</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1602,7 +2008,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1630,7 +2036,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1640,7 +2046,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1651,7 +2057,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -1663,7 +2069,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>12h 9m</t>
+          <t>19h 12m</t>
         </is>
       </c>
     </row>
@@ -1675,7 +2081,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>17h 58m</t>
+          <t>23h 51m</t>
         </is>
       </c>
     </row>
@@ -1712,129 +2118,124 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>IPTV STB box Damage Issue</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -1849,224 +2250,136 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TKT1373949</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>machama maharjan</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>IPTV STB box Damage Issue</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 09:29:55 PM</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 09:25:44 PM</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>18 Oct 2026 10:41:52 AM</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>13h 11m</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>13h 16m</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1373790</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Babu Raja Maharjan</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Damage Issue</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 04:53:20 PM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 04:49:27 PM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>18 Oct 2026 10:37:10 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>17h 43m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>17h 47m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TKT1373790</t>
+          <t>TKT1373949</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Babu Raja Maharjan</t>
+          <t>machama maharjan</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2076,7 +2389,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2096,99 +2409,300 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>17 Oct 2026 04:53:20 PM</t>
+          <t>17 Oct 2026 09:29:55 PM</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>17 Oct 2026 04:49:27 PM</t>
+          <t>17 Oct 2026 09:25:44 PM</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:37:10 AM</t>
+          <t>18 Oct 2026 10:41:52 AM</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>17h 43m</t>
+          <t>13h 11m</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>17h 47m</t>
+          <t>13h 16m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>TKT1373790</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Babu Raja Maharjan</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 04:53:20 PM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 04:49:27 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 10:37:10 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>17h 43m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>17h 47m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1373790</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Babu Raja Maharjan</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 04:53:20 PM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 04:49:27 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 10:37:10 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>17h 43m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>17h 47m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>TKT1373564</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Dharma Ratna shakya</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>18 Oct 2026 10:59:14 AM</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>17 Oct 2026 11:56:46 AM</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>18 Oct 2026 10:59:14 AM</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>23h 2m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1372734</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Ram Dhayal Mahato</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:11:07 PM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:11:07 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:32:58 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1639,20 +1639,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Prabin Mainali</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9851330557</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9851330557</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1734,10 +1728,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -1748,7 +1740,7 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1844,10 +1836,8 @@
           <t>Ram Dhayal Mahato</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9841455936</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9841455936</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1882,10 +1872,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.73283</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.73283</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1941,48 +1929,255 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>L43-5</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.33553</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.33553000000001</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 21m</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 21m</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:52 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373582</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Manohar Budathoki</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Manohar Budathoki</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9851170865</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:52:47 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9851170865</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 12:18:53 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:52:47 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.67018</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur, Kumaripati, Korean Shop, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>sudobhsb81@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>07:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>3,11</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.32149</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>23h 33m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1999,7 +2194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2036,7 +2231,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2046,7 +2241,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2057,7 +2252,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2264,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>19h 12m</t>
+          <t>16h</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2276,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 51m</t>
+          <t>23h 48m</t>
         </is>
       </c>
     </row>
@@ -2122,14 +2317,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2216,14 +2411,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2672,14 +2867,14 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>16 Oct 2026 12:11:07 PM</t>
@@ -2703,6 +2898,73 @@
       <c r="M27" s="5" t="inlineStr">
         <is>
           <t>1d 23h 21m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373582</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Manohar Budathoki</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:52:47 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 12:18:53 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:52:47 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>23h 33m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -483,23 +483,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW8"/>
+  <dimension ref="A1:AW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -517,14 +517,14 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="18" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
@@ -2039,10 +2039,8 @@
           <t>Manohar Budathoki</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9851170865</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9851170865</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2077,10 +2075,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.67018</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.67018</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2136,50 +2132,1089 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>3,11</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.32149</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.32149</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>23h 33m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:17 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372411</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Subarna Lal Maharjan</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Subarna Lal Maharjan</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9851160664</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:57:33 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9851160664</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:57:33 AM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:17:22 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.72614</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Ranibari, Near Dakshinkali Cold Store, Kathmandu, Bagmati, Central, Nepal, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>20:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L18-7</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.3177</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 19m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 19m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:14 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>iptv not working</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372612</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Arjyal</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Arjyal</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9841380245</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:14:55 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841380245</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 10:50:43 AM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:14:55 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Om Hospital &amp; Research Centre Pvt. Ltd. - Private hospital ?????? ??? Kathmandu 44602, Kathmandu, Ne</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>19:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L30-3</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>23h 33m</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 24m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:12 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Exchange my IPTV Device   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Exchange my IPTV Device</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373603</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9843693628</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:12:49 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9843693628</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 12:40:44 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:12:49 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.71839</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>hadi gaun marga, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>janak.adhikari211@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>07:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L5-8</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.33509</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Exchange my IPTV Device   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>23h 32m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Exchange my IPTV Device   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:11 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373459</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Palpa Paudel</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Palpa Paudel</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9841264468</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:11:45 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9841264468</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 10:06:06 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:11:45 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.71391</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Shanti park, Partitar, Kathmandu 44600, ???????? 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>palpa.paudel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>09:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L29-4</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.36242</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 5m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:10 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373364</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Rupa lama</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Rupa lama</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9813496508</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:10:31 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9813496508</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 08:11:35 AM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:10:31 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.716652</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>mulpani cricket ground , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L34-4</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.392235</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 58m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -2194,13 +3229,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -2231,7 +3266,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2241,7 +3276,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -2252,7 +3287,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>91.7%</t>
         </is>
       </c>
     </row>
@@ -2264,7 +3299,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>13h 23m</t>
         </is>
       </c>
     </row>
@@ -2276,7 +3311,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 48m</t>
+          <t>1d 5h 11m</t>
         </is>
       </c>
     </row>
@@ -2317,14 +3352,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -2335,10 +3370,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -2353,10 +3388,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -2411,14 +3446,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -2434,10 +3469,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -2476,7 +3511,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -2491,224 +3526,136 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1373949</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>machama maharjan</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>IPTV STB box Damage Issue</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 09:29:55 PM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 09:25:44 PM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>18 Oct 2026 10:41:52 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>13h 11m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>13h 16m</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1373790</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Babu Raja Maharjan</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Damage Issue</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 04:53:20 PM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 04:49:27 PM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>18 Oct 2026 10:37:10 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>17h 43m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>17h 47m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1373790</t>
+          <t>TKT1373949</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Babu Raja Maharjan</t>
+          <t>machama maharjan</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2718,7 +3665,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2738,64 +3685,64 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>17 Oct 2026 04:53:20 PM</t>
+          <t>17 Oct 2026 09:29:55 PM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>17 Oct 2026 04:49:27 PM</t>
+          <t>17 Oct 2026 09:25:44 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:37:10 AM</t>
+          <t>18 Oct 2026 10:41:52 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>17h 43m</t>
+          <t>13h 11m</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>17h 47m</t>
+          <t>13h 16m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1373564</t>
+          <t>TKT1373790</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Dharma Ratna shakya</t>
+          <t>Babu Raja Maharjan</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2805,54 +3752,54 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:59:14 AM</t>
+          <t>17 Oct 2026 04:53:20 PM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2026 11:56:46 AM</t>
+          <t>17 Oct 2026 04:49:27 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:59:14 AM</t>
+          <t>18 Oct 2026 10:37:10 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 43m</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>23h 2m</t>
+          <t>17h 47m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1372734</t>
+          <t>TKT1373790</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Ram Dhayal Mahato</t>
+          <t>Babu Raja Maharjan</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2872,99 +3819,568 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 12:11:07 PM</t>
+          <t>17 Oct 2026 04:53:20 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 12:11:07 PM</t>
+          <t>17 Oct 2026 04:49:27 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>18 Oct 2026 11:32:58 AM</t>
+          <t>18 Oct 2026 10:37:10 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 21m</t>
+          <t>17h 43m</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 21m</t>
+          <t>17h 47m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>TKT1373564</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Dharma Ratna shakya</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 10:59:14 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:56:46 AM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 10:59:14 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>23h 2m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1372734</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Ram Dhayal Mahato</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:11:07 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:11:07 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 11:32:58 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>TKT1373582</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Manohar Budathoki</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>18 Oct 2026 11:52:47 AM</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>17 Oct 2026 12:18:53 PM</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>18 Oct 2026 11:52:47 AM</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>23h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1372411</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Subarna Lal Maharjan</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:57:33 AM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:57:33 AM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:17:22 PM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>2d 3h 19m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>2d 3h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372612</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Arjyal</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:14:55 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 10:50:43 AM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:14:55 PM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1373603</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Case : Exchange my IPTV Device   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : Exchange my IPTV Device   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:12:49 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 12:40:44 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:12:49 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>23h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373459</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Palpa Paudel</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:11:45 PM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 10:06:06 AM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:11:45 PM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1373364</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Rupa lama</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:10:31 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 08:11:35 AM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:10:31 PM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>1d 3h 58m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2242,10 +2242,8 @@
           <t>Subarna Lal Maharjan</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9851160664</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9851160664</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2280,10 +2278,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.72614</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.72614</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2335,25 +2331,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>L18-7</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.3177</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.3177</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2449,10 +2441,8 @@
           <t>Rajesh Arjyal</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9841380245</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9841380245</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2524,10 +2514,8 @@
           <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
-      <c r="AH10" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH10" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
@@ -2546,10 +2534,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -2560,7 +2546,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2656,10 +2642,8 @@
           <t>Janak Adhikari</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9843693628</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9843693628</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2694,10 +2678,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.71839</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.71839</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2753,25 +2735,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L5-8</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.33509</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.33508999999999</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : Exchange my IPTV Device   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2867,10 +2845,8 @@
           <t>Palpa Paudel</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9841264468</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9841264468</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2905,10 +2881,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.71391</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.71391</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2964,25 +2938,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L29-4</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.36242</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.36242</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3078,10 +3048,8 @@
           <t>Rupa lama</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9813496508</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9813496508</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3116,10 +3084,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.716652</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.716652</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3171,25 +3137,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>L34-4</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.392235</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.392235</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3238,7 +3200,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4082,7 +4044,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -4149,7 +4111,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -4216,7 +4178,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Case : Exchange my IPTV Device   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -4283,7 +4245,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -4350,7 +4312,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW13"/>
+  <dimension ref="A1:AW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3177,6 +3177,213 @@
       <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 2:57 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372925</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Poonam Thapa</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Poonam Thapa</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9848029115</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:51:48 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9848029115</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:51:48 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 02:57:36 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.74773</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Mandir,P8XH+4PF, Tokha,Fisal Tole, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>poonamthapa7777@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>L7-8</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.32958</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>2d 5m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>2d 5m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3435,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -3249,7 +3456,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -3314,14 +3521,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -3408,14 +3615,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3247,10 +3247,8 @@
           <t>Poonam Thapa</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9848029115</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9848029115</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3285,10 +3283,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.74773</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.74773</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3340,25 +3336,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>L7-8</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.32958</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.32958000000001</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW14"/>
+  <dimension ref="A1:AW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3379,6 +3379,109 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 3:23 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr"/>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
+      <c r="AA15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr"/>
+      <c r="AN15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3390,7 +3493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3427,7 +3530,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -3448,7 +3551,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -3560,84 +3663,75 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3743,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -3667,19 +3761,19 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -3695,7 +3789,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -3718,7 +3812,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -3733,224 +3827,128 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1373949</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>machama maharjan</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>IPTV STB box Damage Issue</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 09:29:55 PM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 09:25:44 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>18 Oct 2026 10:41:52 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>13h 11m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>13h 16m</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1373790</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Babu Raja Maharjan</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Router Damage Issue</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 04:53:20 PM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>17 Oct 2026 04:49:27 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>18 Oct 2026 10:37:10 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>17h 43m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>17h 47m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1373790</t>
+          <t>TKT1373949</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Babu Raja Maharjan</t>
+          <t>machama maharjan</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3960,7 +3958,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3980,64 +3978,64 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : stb box faulty   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>17 Oct 2026 04:53:20 PM</t>
+          <t>17 Oct 2026 09:29:55 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>17 Oct 2026 04:49:27 PM</t>
+          <t>17 Oct 2026 09:25:44 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:37:10 AM</t>
+          <t>18 Oct 2026 10:41:52 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>17h 43m</t>
+          <t>13h 11m</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>17h 47m</t>
+          <t>13h 16m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1373564</t>
+          <t>TKT1373790</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Dharma Ratna shakya</t>
+          <t>Babu Raja Maharjan</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -4047,54 +4045,54 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
+          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:59:14 AM</t>
+          <t>17 Oct 2026 04:53:20 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2026 11:56:46 AM</t>
+          <t>17 Oct 2026 04:49:27 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 10:59:14 AM</t>
+          <t>18 Oct 2026 10:37:10 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 43m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>23h 2m</t>
+          <t>17h 47m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1372734</t>
+          <t>TKT1373790</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Ram Dhayal Mahato</t>
+          <t>Babu Raja Maharjan</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -4114,54 +4112,54 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : router damage issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 12:11:07 PM</t>
+          <t>17 Oct 2026 04:53:20 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 12:11:07 PM</t>
+          <t>17 Oct 2026 04:49:27 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>18 Oct 2026 11:32:58 AM</t>
+          <t>18 Oct 2026 10:37:10 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 21m</t>
+          <t>17h 43m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 21m</t>
+          <t>17h 47m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1373582</t>
+          <t>TKT1373564</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Manohar Budathoki</t>
+          <t>Dharma Ratna shakya</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4181,22 +4179,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : iptv issue   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 11:52:47 AM</t>
+          <t>18 Oct 2026 10:59:14 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2026 12:18:53 PM</t>
+          <t>17 Oct 2026 11:56:46 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 11:52:47 AM</t>
+          <t>18 Oct 2026 10:59:14 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -4206,19 +4204,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>23h 33m</t>
+          <t>23h 2m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1372411</t>
+          <t>TKT1372734</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Subarna Lal Maharjan</t>
+          <t>Ram Dhayal Mahato</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -4248,54 +4246,54 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 08:57:33 AM</t>
+          <t>16 Oct 2026 12:11:07 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 08:57:33 AM</t>
+          <t>16 Oct 2026 12:11:07 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>18 Oct 2026 12:17:22 PM</t>
+          <t>18 Oct 2026 11:32:58 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2d 3h 19m</t>
+          <t>1d 23h 21m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>2d 3h 19m</t>
+          <t>1d 23h 21m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1372612</t>
+          <t>TKT1373582</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Rajesh Arjyal</t>
+          <t>Manohar Budathoki</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4315,22 +4313,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 12:14:55 PM</t>
+          <t>18 Oct 2026 11:52:47 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 10:50:43 AM</t>
+          <t>17 Oct 2026 12:18:53 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 12:14:55 PM</t>
+          <t>18 Oct 2026 11:52:47 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -4340,39 +4338,39 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 24m</t>
+          <t>23h 33m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1373603</t>
+          <t>TKT1372411</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Janak Adhikari</t>
+          <t>Subarna Lal Maharjan</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -4382,54 +4380,54 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : Exchange my IPTV Device   has been updated by Chandramani Tharu</t>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>18 Oct 2026 12:12:49 PM</t>
+          <t>16 Oct 2026 08:57:33 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>17 Oct 2026 12:40:44 PM</t>
+          <t>16 Oct 2026 08:57:33 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>18 Oct 2026 12:12:49 PM</t>
+          <t>18 Oct 2026 12:17:22 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 3h 19m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>23h 32m</t>
+          <t>2d 3h 19m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1373459</t>
+          <t>TKT1372612</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Palpa Paudel</t>
+          <t>Rajesh Arjyal</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -4449,22 +4447,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 12:11:45 PM</t>
+          <t>18 Oct 2026 12:14:55 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2026 10:06:06 AM</t>
+          <t>16 Oct 2026 10:50:43 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 12:11:45 PM</t>
+          <t>18 Oct 2026 12:14:55 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -4474,72 +4472,206 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1d 2h 5m</t>
+          <t>2d 1h 24m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>TKT1373603</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : Exchange my IPTV Device   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:12:49 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 12:40:44 PM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:12:49 PM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>23h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373459</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Palpa Paudel</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:11:45 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 10:06:06 AM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:11:45 PM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>TKT1373364</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Rupa lama</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Case : IPTV ISSUE   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>18 Oct 2026 12:10:31 PM</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>17 Oct 2026 08:11:35 AM</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>18 Oct 2026 12:10:31 PM</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>1d 3h 58m</t>
         </is>

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW15"/>
+  <dimension ref="A1:AW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3482,6 +3482,428 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 3:36 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372989</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Tejendra Regmi</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Tejendra Regmi</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9851179207</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:53:54 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9851179207</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:53:54 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 03:36:06 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.72692</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Sarkari Dhara,P8G7+JMW, Samakhusi Marg, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>14:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L22-5</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 42m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 42m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 3:35 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372989</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Tejendra Regmi</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Tejendra Regmi</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9851179207</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:53:54 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9851179207</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:53:54 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 03:36:06 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.72692</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Sarkari Dhara,P8G7+JMW, Samakhusi Marg, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>14:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L22-5</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 42m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 42m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3493,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3502,7 +3924,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3530,7 +3952,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -3540,7 +3962,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -3551,7 +3973,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3985,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>13h 23m</t>
+          <t>18h 40m</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3997,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 5h 11m</t>
+          <t>1d 8h 2m</t>
         </is>
       </c>
     </row>
@@ -3616,14 +4038,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -3724,14 +4146,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -4677,6 +5099,140 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372989</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Tejendra Regmi</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:53:54 PM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:53:54 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 03:36:06 PM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 42m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 42m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1372989</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Tejendra Regmi</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:53:54 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:53:54 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 03:36:06 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 42m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 42m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3549,10 +3549,8 @@
           <t>Tejendra Regmi</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9851179207</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9851179207</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3587,10 +3585,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.72692</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.72692</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -3646,25 +3642,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>L22-5</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3760,10 +3752,8 @@
           <t>Tejendra Regmi</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9851179207</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9851179207</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3798,10 +3788,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.72692</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.72692</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -3857,25 +3845,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>L22-5</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -3924,7 +3908,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5132,7 +5116,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -5199,7 +5183,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW17"/>
+  <dimension ref="A1:AW18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3888,6 +3888,209 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 4:18 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374134</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Baburaja Maharjan</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Baburaja Maharjan</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9801855562</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:18:08 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>LTP9801855562</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 10:23:07 AM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:18:08 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Avens English Boarding School Avens English Boarding School - School 44600 Ring Rd Lalitpur 44700, K</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>9841567276@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>2,1</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>5h 55m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3899,7 +4102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3908,7 +4111,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3936,7 +4139,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -3946,7 +4149,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -3957,7 +4160,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
@@ -3969,7 +4172,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>18h 40m</t>
+          <t>17h 20m</t>
         </is>
       </c>
     </row>
@@ -3981,7 +4184,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 8h 2m</t>
+          <t>1d 6h 10m</t>
         </is>
       </c>
     </row>
@@ -4022,14 +4225,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -4130,14 +4333,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -5217,6 +5420,73 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374134</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Baburaja Maharjan</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:18:08 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 10:23:07 AM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:18:08 PM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>5h 55m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW18"/>
+  <dimension ref="A1:AW20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3955,10 +3955,8 @@
           <t>Baburaja Maharjan</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9801855562</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9801855562</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4048,10 +4046,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -4062,30 +4058,236 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>5h 55m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>5h 55m</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 4:40 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr"/>
+      <c r="V19" s="3" t="inlineStr"/>
+      <c r="W19" s="3" t="inlineStr"/>
+      <c r="X19" s="3" t="inlineStr"/>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr"/>
+      <c r="AA19" s="3" t="inlineStr"/>
+      <c r="AB19" s="3" t="inlineStr"/>
+      <c r="AC19" s="3" t="inlineStr"/>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AM19" s="3" t="inlineStr"/>
+      <c r="AN19" s="3" t="inlineStr"/>
+      <c r="AO19" s="3" t="inlineStr"/>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 4:39 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr"/>
+      <c r="V20" s="3" t="inlineStr"/>
+      <c r="W20" s="3" t="inlineStr"/>
+      <c r="X20" s="3" t="inlineStr"/>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr"/>
+      <c r="AA20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AC20" s="3" t="inlineStr"/>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr"/>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr"/>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr"/>
+      <c r="AM20" s="3" t="inlineStr"/>
+      <c r="AN20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -4111,7 +4313,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4139,7 +4341,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -4160,7 +4362,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>73.7%</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5655,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW20"/>
+  <dimension ref="A1:AW21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4293,6 +4293,213 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 4:53 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371605</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Ramita Pujari</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Ramita Pujari</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9818579073</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:53:14 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9818579073</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:27:33 AM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:53:14 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.711797</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Namrata Stationery &amp; Gift Center, P863+MPJ, Purano Dhalko Marg, Kathmandu 44600, Bagmati, Central, N</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>04:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.304165</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>3d 5h 25m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4304,7 +4511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4313,7 +4520,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4341,7 +4548,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -4351,7 +4558,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -4362,7 +4569,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4581,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>17h 20m</t>
+          <t>16h 11m</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4593,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 6h 10m</t>
+          <t>1d 9h 19m</t>
         </is>
       </c>
     </row>
@@ -4427,14 +4634,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -4535,14 +4742,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -5689,6 +5896,73 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1371605</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Ramita Pujari</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:53:14 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:27:33 AM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:53:14 PM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>3d 5h 25m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4360,10 +4360,8 @@
           <t>Ramita Pujari</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9818579073</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9818579073</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4398,10 +4396,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.711797</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.711797</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -4453,25 +4449,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>2,14</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.304165</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.304165</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4520,7 +4512,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5929,7 +5921,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW21"/>
+  <dimension ref="A1:AW22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4492,6 +4492,213 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 5:31 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONT replacement  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>ONT replacement</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373659</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Lal Bahadur Shrestha</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Lal Bahadur Shrestha</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9802092474</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 05:31:31 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9802092474</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 01:56:51 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 05:31:31 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.72108</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Near Khusibun Judo Hall, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>06:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.305</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONT replacement  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 34m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONT replacement  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4503,7 +4710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4512,7 +4719,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4540,7 +4747,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -4550,7 +4757,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -4561,7 +4768,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4780,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>16h 11m</t>
+          <t>15h 10m</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4792,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 9h 19m</t>
+          <t>1d 8h 58m</t>
         </is>
       </c>
     </row>
@@ -4644,10 +4851,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -4780,10 +4987,10 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -5955,6 +6162,73 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373659</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Lal Bahadur Shrestha</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONT replacement  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONT replacement  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 05:31:31 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 01:56:51 PM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 05:31:31 PM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 34m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_18_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_18_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4559,10 +4559,8 @@
           <t>Lal Bahadur Shrestha</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9802092474</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9802092474</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4597,10 +4595,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.72108</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.72108</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -4652,25 +4648,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>1,16</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.305</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.30500000000001</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : ONT replacement  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -4719,7 +4711,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6195,7 +6187,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Case : ONT replacement  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
